--- a/AAII_Financials/Quarterly/KAOOY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KAOOY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="92">
   <si>
     <t>KAOOY</t>
   </si>
@@ -656,101 +656,105 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="19" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="20" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -787,32 +791,35 @@
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3">
         <v>3005800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2512500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2609100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2302700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2732900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>7247900</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -849,32 +856,35 @@
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="3">
         <v>1962200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1649900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1665600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1464900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1658400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4172700</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -911,32 +921,35 @@
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="3">
         <v>1043500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>862600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>943500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>837800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1074500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3075200</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -959,8 +972,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -997,32 +1011,35 @@
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O12" s="3">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="3">
         <v>109600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>93600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>100400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>103400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>104600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>313400</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1083,8 +1100,11 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1136,17 +1156,20 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1183,32 +1206,35 @@
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O15" s="3">
+      <c r="O15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P15" s="3">
         <v>48600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>43100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>44600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>41800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>41000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>146600</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1228,8 +1254,9 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1266,32 +1293,35 @@
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O17" s="3">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P17" s="3">
         <v>2770400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2364100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2402100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2150300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2495800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>6382300</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1328,32 +1358,35 @@
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3">
         <v>235400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>148400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>207000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>152400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>237100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>865600</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1376,8 +1409,9 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1414,32 +1448,35 @@
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3">
         <v>-17000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>8700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>27700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>17900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>13600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-6600</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1476,32 +1513,35 @@
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3">
         <v>380700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>302900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>385800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>313800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>399600</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1538,8 +1578,8 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1556,14 +1596,17 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
+      <c r="U22" s="3">
+        <v>0</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1600,32 +1643,35 @@
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O23" s="3">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P23" s="3">
         <v>218300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>157100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>234700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>170300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>250700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>859100</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1662,32 +1708,35 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3">
         <v>17600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>31300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>93200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>45700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>58000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>229200</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1748,8 +1797,11 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1786,32 +1838,35 @@
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O26" s="3">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P26" s="3">
         <v>200700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>125800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>141500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>124600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>192700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>629800</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1848,32 +1903,35 @@
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O27" s="3">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P27" s="3">
         <v>196800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>124000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>139100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>121100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>189400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>619600</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1934,8 +1992,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1972,8 +2033,8 @@
       <c r="N29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
+      <c r="O29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P29" s="3">
         <v>0</v>
@@ -1990,14 +2051,17 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>3</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2058,8 +2122,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2120,8 +2187,11 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2158,32 +2228,35 @@
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3">
         <v>17000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-8700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-27700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-17900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-13600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>6600</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2220,32 +2293,35 @@
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O33" s="3">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P33" s="3">
         <v>196800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>124000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>139100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>121100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>189400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>619600</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2306,8 +2382,11 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2344,99 +2423,105 @@
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O35" s="3">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P35" s="3">
         <v>196800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>124000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>139100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>121100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>189400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>619600</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2459,8 +2544,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2483,70 +2569,74 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2009700</v>
+      </c>
+      <c r="E41" s="3">
         <v>2061900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2228900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2275200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1889600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1676200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2069100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1897100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1906600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1897100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1906600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1630600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1783900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1422600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1742500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1745800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2308800</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2584,465 +2674,489 @@
         <v>0</v>
       </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>146300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>145800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>201200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>169500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>41900</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1539200</v>
+      </c>
+      <c r="E43" s="3">
         <v>1599300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1587200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1549100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1538100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1537400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1639600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1572500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1542200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1572500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1542200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1625900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1666900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1455900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1565400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1421400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1502600</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1953100</v>
+      </c>
+      <c r="E44" s="3">
         <v>1864700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1999500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1746800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1734600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1830200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1871500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1898700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1990700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1898700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1990700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2175400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1976500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1915400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1915100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1713200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1566800</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U44" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>272500</v>
+      </c>
+      <c r="E45" s="3">
         <v>163800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>234700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>155100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>237200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>265500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>136100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>196300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>194400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>196300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>194400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>233900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>157600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>148000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>148600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>148500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>143200</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5774600</v>
+      </c>
+      <c r="E46" s="3">
         <v>5777800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6050300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5813700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5399600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5309400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5796700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5564700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5633800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5564700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5633800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5665800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5731200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5087700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5572800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5198300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5563300</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>371900</v>
+      </c>
+      <c r="E47" s="3">
         <v>99600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>358100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>92400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>328900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>329300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>352300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>333500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>334500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>333500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>334500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>334100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>258300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>229700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>223400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>219300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>231100</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3333600</v>
+      </c>
+      <c r="E48" s="3">
         <v>3548100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3670100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3434000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3446500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3675600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3879200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3757700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3968200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3757700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3968200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4298100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4103500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3761300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4010900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3811900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3934200</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1928300</v>
+      </c>
+      <c r="E49" s="3">
         <v>1980600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2078100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1974000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1967600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2036600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2132800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1772900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1810600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1772900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1810600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1902000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1789500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1648800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1706700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1618000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1622200</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3103,8 +3217,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3165,23 +3282,26 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3">
         <v>276800</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F52" s="3">
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3">
         <v>250600</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3203,32 +3323,35 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O52" s="3">
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3">
         <v>374600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>334900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>356600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>341800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>355700</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3289,70 +3412,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>11678900</v>
+      </c>
+      <c r="E54" s="3">
         <v>11959200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>12504500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>11876600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>11486900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>11713100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>12554800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>11720700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>12056100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>11720700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>12056100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>12527700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>12257100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>11062400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>11870400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>11189300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>11706500</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3375,8 +3504,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3399,380 +3529,399 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1677700</v>
+      </c>
+      <c r="E57" s="3">
         <v>1103400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1726300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1099800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1485500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1552900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1670800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1523200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1628000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1523200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1628000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1767300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1730700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1533500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1606600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1498200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1573800</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>443800</v>
+      </c>
+      <c r="E58" s="3">
         <v>299400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>318400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>355500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>201500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>315500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>234500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>220600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>206200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>220600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>206200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>334600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>604300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>571300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>619800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>439800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>179200</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1077900</v>
+      </c>
+      <c r="E59" s="3">
         <v>1243700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1164500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1103600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1198800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1112500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>755800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1111600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1009600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1111600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1009600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>993100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1120000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1072100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1064700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>930600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1145400</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3199400</v>
+      </c>
+      <c r="E60" s="3">
         <v>3305100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3209200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3241300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2885800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2980900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3262800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2855300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2843800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2855300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2843800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3095100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3455000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3176800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3291100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2868500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2898400</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1015600</v>
+      </c>
+      <c r="E61" s="3">
         <v>1251400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1349300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1204900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1407800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1482500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1617500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1572400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1630600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1572400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1630600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1585400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1262200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1084500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1187200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1324400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1666600</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>112700</v>
+      </c>
+      <c r="E62" s="3">
         <v>117600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>135400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>128200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>128600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>135600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>146300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>142100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>145100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>142100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>145100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>155200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>472600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>362800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>384200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>369900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>382200</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3833,8 +3982,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3895,8 +4047,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3957,70 +4112,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4606800</v>
+      </c>
+      <c r="E66" s="3">
         <v>4977100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5015900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4887400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4728900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4924300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5375200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4867600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4933000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4867600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4933000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5173700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5355500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4781100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5023700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4697400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5076000</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4043,8 +4204,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4105,8 +4267,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4167,8 +4332,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4223,14 +4391,17 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-      <c r="U70" s="3" t="s">
-        <v>3</v>
+      <c r="U70" s="3">
+        <v>0</v>
       </c>
       <c r="V70" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4291,70 +4462,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4598900</v>
+      </c>
+      <c r="E72" s="3">
         <v>4570600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5289500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>4762600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>4479200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>4585200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>5049600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>4711300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4998000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4711300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>4998000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>5347100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>5257100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>4603300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>5304100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>5087500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>5371900</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4415,8 +4592,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4477,8 +4657,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4539,70 +4722,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6887000</v>
+      </c>
+      <c r="E76" s="3">
         <v>6786700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7297700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6785200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6564500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6591600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6978200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6657700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6928600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6657700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6928600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7157800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6901600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6281300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>6846600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>6491900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>6630500</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4663,75 +4852,81 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4768,32 +4963,35 @@
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O81" s="3">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P81" s="3">
         <v>196800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>124000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>139100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>121100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>189400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>619600</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4816,70 +5014,74 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>138600</v>
+      </c>
+      <c r="E83" s="3">
         <v>145900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>160200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>150200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>155400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>166300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>173400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>157900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>165000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>157900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>165000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>177900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>162400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>145800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>151100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>143400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>148900</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4940,8 +5142,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5002,8 +5207,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5064,8 +5272,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5126,8 +5337,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5188,70 +5402,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>443000</v>
+      </c>
+      <c r="E89" s="3">
         <v>551200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>440300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>443200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>422200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-24900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>583300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>387300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>451000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>387300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>451000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-21100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>410000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>289700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>255200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-67200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>372600</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5274,70 +5494,74 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-93800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-69400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-122500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-99300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-99200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-68700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-89000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-96200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-98900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-96200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-98900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-97500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-17919000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-17605000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-25593000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-16084000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-17987000</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
+      <c r="U91" s="3">
+        <v>0</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5398,8 +5622,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5460,70 +5687,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-107300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-112700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-97000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-98600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-46700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-86100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-416600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-114600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-126800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-114600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-126800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-113700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-114900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-119200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-164200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-104100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-116900</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5546,70 +5779,74 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E96" s="3">
         <v>3300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>4200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>3900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>4300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>226200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>5800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>228200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>5200</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M96" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
+      <c r="O96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P96" s="3">
         <v>-5500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-216900</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-4700</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-222100</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-4900</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
         <v>0</v>
       </c>
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5670,8 +5907,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5732,8 +5972,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5794,190 +6037,202 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-45200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-277900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-51900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-73800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-132000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-207100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-64800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-244200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>17900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-244200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>17900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-278000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-18200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-443500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-190700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-258600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-40400</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>70100</v>
+      </c>
+      <c r="E101" s="3">
         <v>66000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-43000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>23100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>65200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>25500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-81400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>15400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>98600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>15400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>98600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>87300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-76200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>14200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>90300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>70400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>39600</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>318800</v>
+      </c>
+      <c r="E102" s="3">
         <v>238600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>297100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>338700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>313600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-252100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>58900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>51600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>407300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>51600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>407300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-387300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>200700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-258700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-9400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-359500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>254900</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
